--- a/target/在库差异表.xlsx
+++ b/target/在库差异表.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U132"/>
+  <dimension ref="A1:U114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,7 +1646,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1655,29 +1655,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ZZ01-DP15</t>
+          <t>ZZ02-DP15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>100000785763</v>
+        <v>100000785768</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ZZ5357TXFV464MC1/V2DBM46-BB</t>
+          <t>ZZ1257V464HE1/S7WAV46-ZZ</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45233.38020833334</v>
+        <v>45232.34375</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1740,29 +1740,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>100000785731</v>
+        <v>100000785768</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ZZ1187K501GF1/MCL6V50-T标运</t>
+          <t>ZZ1257V464HE1/S7WAV46-ZZ</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45232.53159722222</v>
+        <v>45232.34375</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ZZ02-DP15</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1839,48 +1839,48 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>100000785768</v>
+        <v>100000787202</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ZZ1257V464HE1/S7WAV46-ZZ</t>
+          <t>ZZ1257V384HB1/S0WAV38-ZZ</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45232.34375</v>
+        <v>45233.34375</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WG1623105038</t>
+          <t>WG9716943010</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>备轮架摇柄</t>
+          <t>左尾灯支架</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WG1623105038/5</t>
+          <t>WG9716943010/B</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>103597</t>
+          <t>101239</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>山东济宁神州工程机械有限公司</t>
+          <t>河北安进汽车零部件制造有限公司</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>供应商山东济宁神州库存不足(成组物料);</t>
+          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -1901,11 +1901,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>212</v>
+        <v>313</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ02-DF02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1924,48 +1924,48 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100000785768</v>
+        <v>100000787674</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ZZ1257V464HE1/S7WAV46-ZZ</t>
+          <t>ZZ4186V391HE1B/W7EDM39-BY</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45232.34375</v>
+        <v>45234.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>WG9725472075</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>左尾灯支架</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>WG9716943010/B</t>
+          <t>WG9725472075/1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>101623</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>河北安进汽车零部件制造有限公司</t>
+          <t>济南福瑞德汽车科技有限公司</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
+          <t>供应商济南福瑞德仓库无库存;</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -1986,21 +1986,21 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>223</v>
+        <v>328</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ZZ01-DP11</t>
+          <t>ZZ02-ZF05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2009,52 +2009,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100000786439</v>
+        <v>100000788202</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ZZ1167N471GC1/M2M7M47-BZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45233.34375</v>
+        <v>45234.396875</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>WG9116316033</t>
+          <t>AZ992555200011</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>支承角板</t>
+          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>WG9116316033/3</t>
+          <t>AZ992555200011/2</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>103132</t>
+          <t>104610</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>青岛德顺昕工贸有限公司</t>
+          <t>温州永森包装有限公司</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
+        <v>202</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2071,21 +2071,21 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>235</v>
+        <v>331</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ZZ01-ZF04</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2094,48 +2094,48 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>100000786439</v>
+        <v>100000788202</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ZZ1167N471GC1/M2M7M47-BZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45233.34375</v>
+        <v>45234.34375</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>752W06100-0001</t>
+          <t>WG9925810001</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MC07冷却模块</t>
+          <t>带侧标志灯7功能组合后灯（左）</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>752W06100-0001/2</t>
+          <t>WG9925810001/1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>105189</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>聊城市德通交通器材制造有限公司</t>
+          <t>浙江嘉利（丽水）工业股份有限公司</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>供应商聊城市德通交通器材制造有限公司库存不足(成组物料);</t>
+          <t>指定供方浙江嘉利库存不足;</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2156,21 +2156,21 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>236</v>
+        <v>332</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2179,48 +2179,48 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100000786507</v>
+        <v>100000788202</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ZZ5187XXYN711GF1/MCU7M71-T标运</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45233.35</v>
+        <v>45234.34375</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>WG9925810002</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>左尾灯支架</t>
+          <t>带侧标志灯7功能组合后灯（右）</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WG9716943010/B</t>
+          <t>WG9925810002/1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>105189</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>河北安进汽车零部件制造有限公司</t>
+          <t>浙江嘉利（丽水）工业股份有限公司</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
+          <t>指定供方浙江嘉利库存不足;</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2241,21 +2241,21 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ01-NS09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2264,48 +2264,48 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100000787202</v>
+        <v>100000789385</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ZZ1257V384HB1/S0WAV38-ZZ</t>
+          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45233.34375</v>
+        <v>45235.34375</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>810W62550-0011</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>左尾灯支架</t>
+          <t>左侧窗玻璃</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>WG9716943010/B</t>
+          <t>810W62550-0011/1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>河北安进汽车零部件制造有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2326,11 +2326,11 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ZZ01-ZF05</t>
+          <t>ZZ01-NS09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2349,52 +2349,52 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100000783371</v>
+        <v>100000789385</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1B/W7EDM36-BZ</t>
+          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45234.34375</v>
+        <v>45235.34375</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AZ992555200011</t>
+          <t>810W62550-0012</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
+          <t>右侧窗玻璃(与左件对称)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AZ992555200011/2</t>
+          <t>810W62550-0012/1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>温州永森包装有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2411,21 +2411,21 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ZZ02-DF02</t>
+          <t>ZZ01-ZF05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2434,52 +2434,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100000787674</v>
+        <v>100000789385</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7EDM39-BY</t>
+          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45234.4</v>
+        <v>45235.34375</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>WG9725472075</t>
+          <t>AZ992555200011</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>WG9725472075/1</t>
+          <t>AZ992555200011/2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>101623</t>
+          <t>104610</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>济南福瑞德汽车科技有限公司</t>
+          <t>温州永森包装有限公司</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>供应商济南福瑞德仓库无库存;</t>
+          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2496,21 +2496,21 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ZZ02-ZF05</t>
+          <t>ZZ01-ZF10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2519,52 +2519,52 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100000788202</v>
+        <v>100000789385</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45234.396875</v>
+        <v>45235.34375</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AZ992555200011</t>
+          <t>WG9925810001</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
+          <t>带侧标志灯7功能组合后灯（左）</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AZ992555200011/2</t>
+          <t>WG9925810001/1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>105189</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>温州永森包装有限公司</t>
+          <t>浙江嘉利（丽水）工业股份有限公司</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
+          <t>指定供方浙江嘉利库存不足;</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2581,21 +2581,21 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ01-ZF10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2604,29 +2604,29 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>100000788202</v>
+        <v>100000789385</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45234.34375</v>
+        <v>45235.34375</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>WG9925810001</t>
+          <t>WG9925810002</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（左）</t>
+          <t>带侧标志灯7功能组合后灯（右）</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>WG9925810001/1</t>
+          <t>WG9925810002/1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2666,11 +2666,11 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>342</v>
+        <v>388</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2680,57 +2680,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ02-NS33</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100000788202</v>
+        <v>100000788256</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>AH1664..20303</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45234.34375</v>
+        <v>45236.36145833333</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>WG9925810002</t>
+          <t>WG9918588017</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（右）</t>
+          <t>GPS/BD天线</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>WG9925810002/1</t>
+          <t>WG9918588017/5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>104082</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>浙江嘉利（丽水）工业股份有限公司</t>
+          <t>上海势航网络科技有限公司</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>指定供方浙江嘉利库存不足;</t>
+          <t>指定供方上海势航库存不足;</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -2751,7 +2751,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2760,62 +2760,62 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ZZ01-NS09</t>
+          <t>ZZ02-NS33</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100000789385</v>
+        <v>100000788256</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
+          <t>AH1664..20303</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45235.34375</v>
+        <v>45236.36145833333</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>810W62550-0011</t>
+          <t>WG9918588018</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>左侧窗玻璃</t>
+          <t>GPRS天线</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>810W62550-0011/1</t>
+          <t>WG9918588018/5</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>104082</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>上海势航网络科技有限公司</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>指定供方上海势航库存不足;</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -2836,7 +2836,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>355</v>
+        <v>411</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2845,62 +2845,62 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ZZ01-NS09</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100000789385</v>
+        <v>100000789640</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
+          <t>ZZ1257V584HE1/V7WCV58-ZZ</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45235.34375</v>
+        <v>45235.63854166667</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>810W62550-0012</t>
+          <t>WG9716943010</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>右侧窗玻璃(与左件对称)</t>
+          <t>左尾灯支架</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>810W62550-0012/1</t>
+          <t>WG9716943010/B</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>101239</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>河北安进汽车零部件制造有限公司</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -2921,7 +2921,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>361</v>
+        <v>412</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ZZ01-ZF05</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2944,11 +2944,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100000789385</v>
+        <v>100000788920</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
@@ -2956,40 +2956,40 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AZ992555200011</t>
+          <t>WG9925810001</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
+          <t>带侧标志灯7功能组合后灯（左）</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AZ992555200011/2</t>
+          <t>WG9925810001/1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>105189</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>温州永森包装有限公司</t>
+          <t>浙江嘉利（丽水）工业股份有限公司</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
+          <t>指定供方浙江嘉利库存不足;</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3029,11 +3029,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100000789385</v>
+        <v>100000788920</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WG9925810001</t>
+          <t>WG9925810002</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（左）</t>
+          <t>带侧标志灯7功能组合后灯（右）</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>WG9925810001/1</t>
+          <t>WG9925810002/1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3091,11 +3091,11 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>364</v>
+        <v>527</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3110,52 +3110,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100000789385</v>
+        <v>100000789097</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ZZ4256V364HE1H/R7GDM36-ZZ</t>
+          <t>ZZ1257N56CGF1/MCF7M56-标运</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45235.34375</v>
+        <v>45236.57534722222</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WG9925810002</t>
+          <t>WG9716943010</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（右）</t>
+          <t>左尾灯支架</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>WG9925810002/1</t>
+          <t>WG9716943010/B</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>101239</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>浙江嘉利（丽水）工业股份有限公司</t>
+          <t>河北安进汽车零部件制造有限公司</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>指定供方浙江嘉利库存不足;</t>
+          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -3176,11 +3176,11 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>411</v>
+        <v>566</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3190,57 +3190,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ZZ02-NS33</t>
+          <t>ZZ02-NS10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100000788256</v>
+        <v>100000789039</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AH1664..20303</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45236.36145833333</v>
+        <v>45236.3875</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>WG9918588017</t>
+          <t>810W62550-0011</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>GPS/BD天线</t>
+          <t>左侧窗玻璃</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>WG9918588017/5</t>
+          <t>810W62550-0011/1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>104082</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>上海势航网络科技有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>指定供方上海势航库存不足;</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -3261,11 +3261,11 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>412</v>
+        <v>567</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3275,57 +3275,57 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZZ02-NS33</t>
+          <t>ZZ02-NS10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100000788256</v>
+        <v>100000789039</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AH1664..20303</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45236.36145833333</v>
+        <v>45236.3875</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>WG9918588018</t>
+          <t>810W62550-0012</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>GPRS天线</t>
+          <t>右侧窗玻璃(与左件对称)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>WG9918588018/5</t>
+          <t>810W62550-0012/1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>104082</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>上海势航网络科技有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>指定供方上海势航库存不足;</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -3346,11 +3346,11 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>436</v>
+        <v>589</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3360,61 +3360,61 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ02-ZF05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100000789640</v>
+        <v>100000789039</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ZZ1257V584HE1/V7WCV58-ZZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45235.63854166667</v>
+        <v>45236.3875</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>AZ992555200011</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>左尾灯支架</t>
+          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>WG9716943010/B</t>
+          <t>AZ992555200011/2</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>104610</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>河北安进汽车零部件制造有限公司</t>
+          <t>温州永森包装有限公司</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
+          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3431,11 +3431,11 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>437</v>
+        <v>590</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100000788920</v>
+        <v>100000789039</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45235.34375</v>
+        <v>45236.34375</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3516,11 +3516,11 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>438</v>
+        <v>591</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100000788920</v>
+        <v>100000789039</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45235.34375</v>
+        <v>45236.34375</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3601,11 +3601,11 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>559</v>
+        <v>656</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ01-DP11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3624,48 +3624,48 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100000789097</v>
+        <v>100000791626</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ZZ1257N56CGF1/MCF7M56-标运</t>
+          <t>ZZ1167N471GC1/M2M7M47-BZ</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45236.57534722222</v>
+        <v>45237.72916666666</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>WG9116316033</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>左尾灯支架</t>
+          <t>支承角板</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>WG9716943010/B</t>
+          <t>WG9116316033/3</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>河北安进汽车零部件制造有限公司</t>
+          <t>青岛德顺昕工贸有限公司</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>供应商河北安进汽车零部件制造有限公司库存不足(成组物料);</t>
+          <t>供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -3686,71 +3686,71 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>600</v>
+        <v>686</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ZZ02-NS10</t>
+          <t>ZZ01-NS02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100000789039</v>
+        <v>100000791724</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ4257V384GF1LB/W9UDV38-T标运</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45236.3875</v>
+        <v>45237.53784722222</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>810W62550-0011</t>
+          <t>711W61900-7132</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>左侧窗玻璃</t>
+          <t>过滤器系统总成</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>810W62550-0011/1</t>
+          <t>711W61900-7132/4</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>湖北美瑞特空调系统有限公司</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>供应商湖北美瑞特空调系统库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -3771,71 +3771,71 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>601</v>
+        <v>687</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ZZ02-NS10</t>
+          <t>ZZ01-NS02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100000789039</v>
+        <v>100000791724</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ4257V384GF1LB/W9UDV38-T标运</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45236.3875</v>
+        <v>45237.53784722222</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>810W62550-0012</t>
+          <t>AZ166482001032</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>右侧窗玻璃(与左件对称)</t>
+          <t>控制面板总成(CAN+三态压力开关)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>810W62550-0012/1</t>
+          <t>AZ166482001032/5</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>湖北美瑞特空调系统有限公司</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>供应商湖北美瑞特空调系统库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -3856,21 +3856,21 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>624</v>
+        <v>720</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ZZ02-ZF05</t>
+          <t>ZZ01-NS09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100000789039</v>
+        <v>100000791639</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3887,44 +3887,44 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45236.3875</v>
+        <v>45237.34375</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AZ992555200011</t>
+          <t>810W62550-0011</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>油箱拉带复紧警告标识(大方/曼/中俄文)</t>
+          <t>左侧窗玻璃</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>AZ992555200011/2</t>
+          <t>810W62550-0011/1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>104610</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>温州永森包装有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>供应商温州永森物料AZ992555200011##库存不足一台份;</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3941,21 +3941,21 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>625</v>
+        <v>721</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ01-NS09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100000789039</v>
+        <v>100000791639</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3972,40 +3972,40 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45236.34375</v>
+        <v>45237.34375</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>WG9925810001</t>
+          <t>810W62550-0012</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（左）</t>
+          <t>右侧窗玻璃(与左件对称)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>WG9925810001/1</t>
+          <t>810W62550-0012/1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>浙江嘉利（丽水）工业股份有限公司</t>
+          <t>江苏铁锚科技股份有限公司</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>指定供方浙江嘉利库存不足;</t>
+          <t>供应商江苏铁锚仓库无库存;</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -4026,21 +4026,21 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>626</v>
+        <v>779</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ZZ02-ZF10</t>
+          <t>ZZ01-ZF10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100000789039</v>
+        <v>100000791639</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45236.34375</v>
+        <v>45237.34375</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>WG9925810002</t>
+          <t>WG9925810001</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（右）</t>
+          <t>带侧标志灯7功能组合后灯（左）</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>WG9925810002/1</t>
+          <t>WG9925810001/1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>692</v>
+        <v>780</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4125,57 +4125,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ZZ01-DP11</t>
+          <t>ZZ01-ZF10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>100000791626</v>
+        <v>100000791639</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ZZ1167N471GC1/M2M7M47-BZ</t>
+          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45237.72916666666</v>
+        <v>45237.34375</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>WG9116316033</t>
+          <t>WG9925810002</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>支承角板</t>
+          <t>带侧标志灯7功能组合后灯（右）</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>WG9116316033/3</t>
+          <t>WG9925810002/1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>103132</t>
+          <t>105189</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>青岛德顺昕工贸有限公司</t>
+          <t>浙江嘉利（丽水）工业股份有限公司</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>指定供方浙江嘉利库存不足;</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -4196,11 +4196,11 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>743</v>
+        <v>1208</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ZZ01-NS02</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4219,55 +4219,55 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100000791724</v>
+        <v>100000793243</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ZZ4257V384GF1LB/W9UDV38-T标运</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45237.53784722222</v>
+        <v>45239.54722222222</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>711W61900-7132</t>
+          <t>752W41615-5015</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>过滤器系统总成</t>
+          <t>左踏板支架焊接总成</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>711W61900-7132/4</t>
+          <t>752W41615-5015/1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>101455</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>湖北美瑞特空调系统有限公司</t>
+          <t>黄骅渤海机械制造有限公司</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>供应商湖北美瑞特空调系统库存不足(成组物料);</t>
+          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商诸城盛开达仓库无库存;</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4281,11 +4281,11 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>745</v>
+        <v>1209</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ZZ01-NS02</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4304,39 +4304,39 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100000791724</v>
+        <v>100000793221</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ZZ4257V384GF1LB/W9UDV38-T标运</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45237.53784722222</v>
+        <v>45239.52847222222</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AZ166482001032</t>
+          <t>752W41615-5015</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>控制面板总成(CAN+三态压力开关)</t>
+          <t>左踏板支架焊接总成</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>AZ166482001032/5</t>
+          <t>752W41615-5015/2</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>湖北美瑞特空调系统有限公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>供应商湖北美瑞特空调系统库存不足(成组物料);</t>
+          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4366,11 +4366,11 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>792</v>
+        <v>1212</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4380,57 +4380,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ZZ01-NS05</t>
+          <t>ZZ01-DF02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100000791763</v>
+        <v>100000793147</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ZZ1167N621GC1/M2M7M62-BY</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45237.76041666666</v>
+        <v>45239.47569444445</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>WG9918588091</t>
+          <t>850W41720-5025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>四方位影像系统驾驶室电器装置（TX/T5G）</t>
+          <t>低地板驾驶室前悬摆臂支架总成</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>WG9918588091/2</t>
+          <t>850W41720-5025/3</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>100167</t>
+          <t>101753</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>北京万里科济数控技术有限公司</t>
+          <t>济南汇英机械有限公司</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>限定或订单一致性供应商100167&lt;br /&gt;100167无库存;</t>
+          <t>供应商济南汇英仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -4451,11 +4451,11 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>799</v>
+        <v>1249</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ZZ01-NS09</t>
+          <t>ZZ01-DP15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4474,52 +4474,52 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100000791639</v>
+        <v>100000793122</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45237.34375</v>
+        <v>45239.34375</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>810W62550-0011</t>
+          <t>AZ992555500029</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>左侧窗玻璃</t>
+          <t>轻量化油箱支架(675×500截面油箱)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>810W62550-0011/1</t>
+          <t>AZ992555500029/2</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>101623</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>济南福瑞德汽车科技有限公司</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>供应商济南福瑞德物料AZ992555500029##库存不足一台份&lt;br /&gt;供应商青岛宇远仓库无库存;</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -4536,11 +4536,11 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>800</v>
+        <v>1269</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4550,64 +4550,64 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ZZ01-NS09</t>
+          <t>ZZ01-ND05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100000791639</v>
+        <v>100000793172</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45237.34375</v>
+        <v>45239.60347222222</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>810W62550-0012</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>右侧窗玻璃(与左件对称)</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>810W62550-0012/1</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>江苏铁锚科技股份有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>供应商江苏铁锚仓库无库存;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4621,11 +4621,11 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>940</v>
+        <v>1270</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4635,61 +4635,61 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ01-ND05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100000791639</v>
+        <v>100000793221</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45237.34375</v>
+        <v>45239.52847222222</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>WG9925810001</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（左）</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>WG9925810001/1</t>
+          <t>811W41722-6022/3</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>104206</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>浙江嘉利（丽水）工业股份有限公司</t>
+          <t>十堰东风采埃孚减振器有限公司</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>指定供方浙江嘉利库存不足;</t>
+          <t>供应商东风采埃孚物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商江苏环球洪浩物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -4706,11 +4706,11 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>941</v>
+        <v>1308</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ZZ01-ZF10</t>
+          <t>ZZ01-NS14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4729,48 +4729,48 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100000791639</v>
+        <v>100000793122</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ZZ4186V391HE1B/W7GBM39-BZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45237.34375</v>
+        <v>45239.34375</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>WG9925810002</t>
+          <t>810W26400-6353</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>带侧标志灯7功能组合后灯（右）</t>
+          <t>刮水器总成</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>WG9925810002/1</t>
+          <t>810W26400-6353/1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>105189</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>浙江嘉利（丽水）工业股份有限公司</t>
+          <t>浙江胜华波电器股份有限公司</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>指定供方浙江嘉利库存不足;</t>
+          <t>供应商浙江胜华波库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -4791,7 +4791,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1408</v>
+        <v>1315</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-NS23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100000793243</v>
+        <v>100000793172</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4822,47 +4822,47 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45239.54722222222</v>
+        <v>45239.60347222222</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>752W41615-5015</t>
+          <t>712W28230-0007</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>左踏板支架焊接总成</t>
+          <t>控制器+遥控器（TX标配/马步奇电机）</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>752W41615-5015/1</t>
+          <t>712W28230-0007/1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>101455</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>黄骅渤海机械制造有限公司</t>
+          <t>北京经纬恒润科技股份有限公司</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商诸城盛开达仓库无库存;</t>
+          <t>供应商北京经纬恒润库存不足(成组物料/订单一致性);</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1409</v>
+        <v>1320</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4890,16 +4890,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-NS38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100000793221</v>
+        <v>100000793122</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4907,40 +4907,40 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45239.52847222222</v>
+        <v>45239.34375</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>752W41615-5015</t>
+          <t>810W26430-6068</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>左踏板支架焊接总成</t>
+          <t>刮臂总成</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>752W41615-5015/2</t>
+          <t>810W26430-6068/1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>济南金瑞阳机械制造有限公司</t>
+          <t>浙江胜华波电器股份有限公司</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商诸城盛开达仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
+          <t>供应商浙江胜华波库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -4961,7 +4961,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1410</v>
+        <v>1336</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-ZD01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100000793243</v>
+        <v>100000793120</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4992,47 +4992,47 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45239.54722222222</v>
+        <v>45239.44444444445</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>752W41615-5016</t>
+          <t>WG9000360714</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>右踏板支架焊接总成</t>
+          <t>储气筒总成Φ275/40L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>752W41615-5016/1</t>
+          <t>WG9000360714/4</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>101455</t>
+          <t>101688</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>黄骅渤海机械制造有限公司</t>
+          <t>济南亨利元汽车零配件有限公司</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商诸城盛开达仓库无库存;</t>
+          <t>供应商济南亨利元仓库无库存&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>1411</v>
+        <v>1337</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-ZD01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100000793221</v>
+        <v>100000793240</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5077,44 +5077,44 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45239.52847222222</v>
+        <v>45239.42569444444</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>752W41615-5016</t>
+          <t>WG9000360714</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>右踏板支架焊接总成</t>
+          <t>储气筒总成Φ275/40L</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>752W41615-5016/2</t>
+          <t>WG9000360714/6</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>137050</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>济南金瑞阳机械制造有限公司</t>
+          <t>重庆市亚华汽车配件有限责任公司</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商诸城盛开达仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
+          <t>供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南亨利元仓库无库存;</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>1414</v>
+        <v>1452</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ZZ01-DF02</t>
+          <t>ZZ02-DF02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5154,15 +5154,15 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100000793147</v>
+        <v>100000793048</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45239.47569444445</v>
+        <v>45239.45069444444</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>850W41720-5025/3</t>
+          <t>850W41720-5025/4</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>115280</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>济南汇英机械有限公司</t>
+          <t>文安县北方谊联汽车零部件有限公司</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;,供应商济南汇英仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -5216,7 +5216,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>1454</v>
+        <v>1497</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -5225,12 +5225,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ZZ01-DP15</t>
+          <t>ZZ02-DP04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5239,52 +5239,52 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100000793122</v>
+        <v>100000793036</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ4187V501HF1L/B9GDV50-新标运</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45239.34375</v>
+        <v>45239.353125</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AZ992555500029</t>
+          <t>WG9116316033</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>轻量化油箱支架(675×500截面油箱)</t>
+          <t>支承角板</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>AZ992555500029/2</t>
+          <t>WG9116316033/3</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>101623</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>济南福瑞德汽车科技有限公司</t>
+          <t>青岛德顺昕工贸有限公司</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>供应商济南福瑞德物料AZ992555500029##库存不足一台份&lt;br /&gt;供应商青岛宇远仓库无库存;</t>
+          <t>供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>1475</v>
+        <v>1561</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ZZ01-ND05</t>
+          <t>ZZ02-DP19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5324,55 +5324,55 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100000793172</v>
+        <v>100000793031</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ4257W324HF1B/ZCGEV34-新标重</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45239.60347222222</v>
+        <v>45239.43194444444</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>AZ9X25939527</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>左侧隔音板前支架</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>AZ9X25939527/2</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>104801</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>新乡市新平航空机械有限公司</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商新平机械物料AZ9X25939527##库存不足一台份&lt;br /&gt;供应商聊城昌吾仓库无库存;</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>1476</v>
+        <v>1599</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZZ01-ND05</t>
+          <t>ZZ02-ND05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5409,15 +5409,15 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100000793221</v>
+        <v>100000793048</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45239.52847222222</v>
+        <v>45239.42569444444</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5431,33 +5431,33 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>811W41722-6022/3</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>104206</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>十堰东风采埃孚减振器有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>供应商东风采埃孚物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商江苏环球洪浩物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>1514</v>
+        <v>1661</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5480,29 +5480,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ZZ01-NS14</t>
+          <t>ZZ02-NS03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100000793122</v>
+        <v>100000793048</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45239.34375</v>
+        <v>45239.44131944444</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>1521</v>
+        <v>1724</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5565,62 +5565,62 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ZZ01-NS23</t>
+          <t>ZZ02-NS14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100000793122</v>
+        <v>100000793067</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45239.34375</v>
+        <v>45239.54409722222</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>712W28230-0007</t>
+          <t>810W26400-6353</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>控制器+遥控器（TX标配/马步奇电机）</t>
+          <t>刮水器总成</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>712W28230-0007/1</t>
+          <t>810W26400-6353/1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>北京经纬恒润科技股份有限公司</t>
+          <t>浙江胜华波电器股份有限公司</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>供应商北京经纬恒润库存不足(成组物料/订单一致性);</t>
+          <t>供应商浙江胜华波库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -5641,7 +5641,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>1526</v>
+        <v>1754</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5650,29 +5650,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ZZ01-NS38</t>
+          <t>ZZ02-NS32</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100000793122</v>
+        <v>100000793048</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45239.34375</v>
+        <v>45239.45069444444</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>1541</v>
+        <v>1755</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ZZ01-ZD01</t>
+          <t>ZZ02-NS32</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5749,48 +5749,48 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100000793128</v>
+        <v>100000793051</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45239.40625</v>
+        <v>45239.57222222222</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>752W51715-0024</t>
+          <t>810W26440-0063</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>储气筒支架(φ276)</t>
+          <t>刮片</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>752W51715-0024/5</t>
+          <t>810W26440-0063/1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>102724</t>
+          <t>105216</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>莱州市光州路金昌模具加工厂</t>
+          <t>浙江胜华波电器股份有限公司</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>供应商莱州金昌仓库无库存&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南杰安永泰物料752W51715-0024##库存不足一台份&lt;br /&gt;供应商济南中宝泉仓库无库存;</t>
+          <t>供应商浙江胜华波库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -5811,7 +5811,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>1543</v>
+        <v>1794</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5820,12 +5820,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ZZ01-ZD01</t>
+          <t>ZZ02-NW03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5834,48 +5834,48 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100000793120</v>
+        <v>100000792747</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45239.44444444445</v>
+        <v>45239.48819444444</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>WG9000360714</t>
+          <t>711W61900-7134</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>储气筒总成Φ275/40L</t>
+          <t>空调机总成</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>WG9000360714/4</t>
+          <t>711W61900-7134/8</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>101688</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>济南亨利元汽车零配件有限公司</t>
+          <t>湖北美标汽车制冷系统有限公司</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>供应商济南亨利元仓库无库存&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份;</t>
+          <t>供应商湖北美标汽车制冷系统库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -5896,7 +5896,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>1544</v>
+        <v>1818</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5905,12 +5905,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ZZ01-ZD01</t>
+          <t>ZZ02-ZD01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5919,52 +5919,52 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100000793240</v>
+        <v>100000792736</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45239.42569444444</v>
+        <v>45239.53159722222</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>WG9000360714</t>
+          <t>WG9000360782</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>储气筒总成Φ275/40L</t>
+          <t>铝合金储气筒总成Φ276/40L</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>WG9000360714/6</t>
+          <t>WG9000360782/1</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>137050</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>重庆市亚华汽车配件有限责任公司</t>
+          <t>淄博鲁川汽车配件有限公司</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南亨利元仓库无库存;</t>
+          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>1625</v>
+        <v>1819</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -5990,12 +5990,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ZZ01-ZZ03</t>
+          <t>ZZ02-ZD01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6004,48 +6004,48 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100000793144</v>
+        <v>100000793821</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45239.46319444444</v>
+        <v>45239.55034722222</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>WG9725543351</t>
+          <t>WG9000360782</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>上限位板</t>
+          <t>铝合金储气筒总成Φ276/40L</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>WG9725543351/4</t>
+          <t>WG9000360782/3</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>102007</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>济南杰安永泰机械设备有限公司</t>
+          <t>济南润友模塑有限公司</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>供应商济南杰安永泰仓库无库存&lt;br /&gt;供应商汇泉机械物料WG9725543351##库存不足一台份&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>1664</v>
+        <v>1917</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ZZ02-DF02</t>
+          <t>ZZ02-ZF07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6101,43 +6101,43 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>850W41720-5025</t>
+          <t>YG9725190070</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>低地板驾驶室前悬摆臂支架总成</t>
+          <t>油滤器后支架</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>850W41720-5025/4</t>
+          <t>YG9725190070/2</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>115280</t>
+          <t>101455</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>文安县北方谊联汽车零部件有限公司</t>
+          <t>黄骅渤海机械制造有限公司</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>1709</v>
+        <v>1945</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6165,57 +6165,57 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ZZ02-DP04</t>
+          <t>ZZ02-ZZ00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>100000793036</v>
+        <v>100000793825</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ZZ4187V501HF1L/B9GDV50-新标运</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45239.353125</v>
+        <v>45239.55347222222</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>WG9116316033</t>
+          <t>WG9925860020</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>支承角板</t>
+          <t>备胎支架焊接总成</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>WG9116316033/3</t>
+          <t>WG9925860020/3</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>103132</t>
+          <t>102034</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>青岛德顺昕工贸有限公司</t>
+          <t>济南圣凯工贸有限公司</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商济南圣凯仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -6236,21 +6236,21 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>1773</v>
+        <v>2069</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ZZ02-DP19</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6259,52 +6259,52 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>100000793031</v>
+        <v>100000794030</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ZZ4257W324HF1B/ZCGEV34-新标重</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45239.43194444444</v>
+        <v>45240.68854166667</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AZ9X25939527</t>
+          <t>752W41615-5015</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>左侧隔音板前支架</t>
+          <t>左踏板支架焊接总成</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>AZ9X25939527/2</t>
+          <t>752W41615-5015/2</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>104801</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>新乡市新平航空机械有限公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>供应商新平机械物料AZ9X25939527##库存不足一台份&lt;br /&gt;供应商聊城昌吾仓库无库存;</t>
+          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -6321,21 +6321,21 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>1814</v>
+        <v>2070</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ZZ02-ND05</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6344,55 +6344,55 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>100000793048</v>
+        <v>100000794059</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45239.42569444444</v>
+        <v>45240.70729166667</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>752W41615-5015</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>左踏板支架焊接总成</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>752W41615-5015/3</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>105461</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>诸城市盛开达汽车部件有限公司</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6406,21 +6406,21 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>1877</v>
+        <v>2071</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ZZ02-NS03</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6429,48 +6429,48 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>100000793048</v>
+        <v>100000794037</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45239.44131944444</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>810W26400-6353</t>
+          <t>752W41615-5016</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>刮水器总成</t>
+          <t>右踏板支架焊接总成</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>810W26400-6353/1</t>
+          <t>752W41615-5016/3</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>105216</t>
+          <t>105461</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>浙江胜华波电器股份有限公司</t>
+          <t>诸城市盛开达汽车部件有限公司</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>供应商浙江胜华波库存不足(成组物料);</t>
+          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -6491,21 +6491,21 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>1940</v>
+        <v>2074</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ZZ02-NS14</t>
+          <t>ZZ01-DF01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6514,52 +6514,52 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>100000793067</v>
+        <v>100000794011</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45239.54409722222</v>
+        <v>45240.66979166667</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>810W26400-6353</t>
+          <t>WG9731520059</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>刮水器总成</t>
+          <t>加强板总成</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>810W26400-6353/1</t>
+          <t>WG9731520059/3</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>105216</t>
+          <t>115280</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>浙江胜华波电器股份有限公司</t>
+          <t>文安县北方谊联汽车零部件有限公司</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>供应商浙江胜华波库存不足(成组物料);</t>
+          <t>供应商文安县北方谊联汽车零部件有限公司物料WG9731520059##库存不足一台份&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -6576,21 +6576,21 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>1970</v>
+        <v>2075</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ZZ02-NS32</t>
+          <t>ZZ01-DF02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6599,55 +6599,55 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>100000793048</v>
+        <v>100000794037</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45239.45069444444</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>810W26430-6068</t>
+          <t>850W41720-5025</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>刮臂总成</t>
+          <t>低地板驾驶室前悬摆臂支架总成</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>810W26430-6068/1</t>
+          <t>850W41720-5025/2</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>105216</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>浙江胜华波电器股份有限公司</t>
+          <t>济南豪曼汽车配件有限公司</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>供应商浙江胜华波库存不足(成组物料);</t>
+          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -6661,21 +6661,21 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>1971</v>
+        <v>2079</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ZZ02-NS32</t>
+          <t>ZZ01-DF02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6684,52 +6684,52 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100000793051</v>
+        <v>100000794037</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45239.57222222222</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>810W26440-0063</t>
+          <t>WG9931470260</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>刮片</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>810W26440-0063/1</t>
+          <t>WG9931470260/1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>105216</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>浙江胜华波电器股份有限公司</t>
+          <t>济南市中海兴汽车配件厂</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>供应商浙江胜华波库存不足(成组物料);</t>
+          <t>供应商济南海兴物料WG9931470260##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -6746,21 +6746,21 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>2010</v>
+        <v>2121</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ZZ02-NW03</t>
+          <t>ZZ01-DP15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6769,48 +6769,48 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>100000792747</v>
+        <v>100000794037</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45239.48819444444</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>711W61900-7134</t>
+          <t>AZ992555500029</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>空调机总成</t>
+          <t>轻量化油箱支架(675×500截面油箱)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>711W61900-7134/8</t>
+          <t>AZ992555500029/1</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>103264</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>湖北美标汽车制冷系统有限公司</t>
+          <t>青岛宇远新材料有限公司</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>供应商湖北美标汽车制冷系统库存不足(成组物料);</t>
+          <t>供应商青岛宇远仓库无库存&lt;br /&gt;供应商济南福瑞德物料AZ992555500029##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -6831,21 +6831,21 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>2034</v>
+        <v>2128</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ZZ02-ZD01</t>
+          <t>ZZ01-DP19</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6854,52 +6854,52 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>100000793068</v>
+        <v>100000794012</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ4257V424KF1L/W9EDV38-标运创富</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45239.48506944445</v>
+        <v>45240.43506944444</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>WG9000360782</t>
+          <t>YZ952536000197</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>铝合金储气筒总成Φ276/40L</t>
+          <t>中/后桥管束支架（汉德425ZGY）</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>WG9000360782/1</t>
+          <t>YZ952536000197/2</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>103647</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>淄博鲁川汽车配件有限公司</t>
+          <t>山东鲲乾汽车配件有限公司</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
+          <t>供应商鲲乾汽配物料YZ952536000197##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -6916,21 +6916,21 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>2035</v>
+        <v>2155</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ZZ02-ZD01</t>
+          <t>ZZ01-ND05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6939,55 +6939,55 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100000792736</v>
+        <v>100000794037</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45239.53159722222</v>
+        <v>45240.54722222222</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>WG9000360782</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>铝合金储气筒总成Φ276/40L</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>WG9000360782/3</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>102007</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>济南润友模塑有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -7001,21 +7001,21 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>2138</v>
+        <v>2214</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ZZ02-ZF07</t>
+          <t>ZZ01-NS23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7024,55 +7024,55 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>100000793048</v>
+        <v>100000794037</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45239.45069444444</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>YG9725190070</t>
+          <t>712W28230-0007</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>油滤器后支架</t>
+          <t>控制器+遥控器（TX标配/马步奇电机）</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>YG9725190070/2</t>
+          <t>712W28230-0007/1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>101455</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>黄骅渤海机械制造有限公司</t>
+          <t>北京经纬恒润科技股份有限公司</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
+          <t>供应商北京经纬恒润库存不足(成组物料/订单一致性);</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -7086,78 +7086,78 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>2140</v>
+        <v>2236</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ZZ02-ZF08</t>
+          <t>ZZ01-ZD01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>100000792745</v>
+        <v>100000794037</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ZZ3317V486HF1/CCWDM44-超强</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45239.34375</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>WG9100360787</t>
+          <t>WG9000360714</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>铝制储气筒总成Φ206/5L</t>
+          <t>储气筒总成Φ275/40L</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>WG9100360787/1</t>
+          <t>WG9000360714/6</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>137050</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>淄博鲁川汽车配件有限公司</t>
+          <t>重庆市亚华汽车配件有限责任公司</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南亨利元仓库无库存&lt;br /&gt;供应商重庆市亚华汽车配件有仓库无库存;</t>
+          <t>供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南亨利元仓库无库存;</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -7171,75 +7171,75 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>2168</v>
+        <v>2294</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ZZ02-ZZ00</t>
+          <t>ZZ01-ZF01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>100000793825</v>
+        <v>100000794024</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ4257V344KF1/WCEDV32-标运创富</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45239.55347222222</v>
+        <v>45240.38125</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>WG9925860020</t>
+          <t>YZ952555000148</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>备胎支架焊接总成</t>
+          <t>油箱拉带(700×700截面油箱)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>WG9925860020/3</t>
+          <t>YZ952555000148/3</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>102034</t>
+          <t>103289</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>济南圣凯工贸有限公司</t>
+          <t>清河县捷迈汽车零部件有限公司</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>供应商济南圣凯仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
+          <t>供应商清河捷迈物料YZ952555000148##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>2291</v>
+        <v>2310</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-ZF04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7291,27 +7291,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>752W41615-5015</t>
+          <t>YZ160082120020</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>左踏板支架焊接总成</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>752W41615-5015/3</t>
+          <t>YZ160082120020/2</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>105461</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>诸城市盛开达汽车部件有限公司</t>
+          <t>济南市中海兴汽车配件厂</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
+          <t>供应商济南海兴仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存;</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>2292</v>
+        <v>2316</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -7355,16 +7355,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-ZF06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>100000794037</v>
+        <v>100000794009</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7372,40 +7372,40 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.76354166667</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>752W41615-5016</t>
+          <t>811W41722-6032</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>右踏板支架焊接总成</t>
+          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>752W41615-5016/3</t>
+          <t>811W41722-6032/1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>105461</t>
+          <t>104290</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>诸城市盛开达汽车部件有限公司</t>
+          <t>隆昌山川机械有限责任公司</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>供应商诸城盛开达仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
+          <t>供应商山川减振器仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份&lt;br /&gt;供应商江苏环球洪浩仓库无库存;</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -7426,7 +7426,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>2295</v>
+        <v>2317</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ZZ01-DF01</t>
+          <t>ZZ01-ZF06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100000794011</v>
+        <v>100000794030</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7457,44 +7457,44 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45240.66979166667</v>
+        <v>45240.68854166667</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>WG9731520059</t>
+          <t>811W41722-6032</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>加强板总成</t>
+          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>WG9731520059/3</t>
+          <t>811W41722-6032/2</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>115280</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>文安县北方谊联汽车零部件有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>供应商文安县北方谊联汽车零部件有限公司物料WG9731520059##库存不足一台份&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
+          <t>供应商江苏环球洪浩仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份&lt;br /&gt;供应商山川减振器仓库无库存;</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>2296</v>
+        <v>2318</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ZZ01-DF02</t>
+          <t>ZZ01-ZF07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7546,36 +7546,36 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>850W41720-5025</t>
+          <t>WG9X25190066</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>低地板驾驶室前悬摆臂支架总成</t>
+          <t>空滤器总成</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>850W41720-5025/2</t>
+          <t>WG9X25190066/1</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>102912</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>济南豪曼汽车配件有限公司</t>
+          <t>曼胡默尔滤清器（济南）有限公司</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存;</t>
+          <t>供应商曼胡仓库无库存&lt;br /&gt;供应商河北亿利仓库无库存&lt;br /&gt;供应商平原滤清器仓库无库存;</t>
         </is>
       </c>
       <c r="Q84" t="n">
@@ -7596,7 +7596,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>2300</v>
+        <v>2319</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ZZ01-DF02</t>
+          <t>ZZ01-ZF07</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>100000794037</v>
+        <v>100000794008</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7627,44 +7627,44 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.63854166667</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>WG9931470260</t>
+          <t>WG9X25190066</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>空滤器总成</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>WG9931470260/1</t>
+          <t>WG9X25190066/3</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>102096</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>济南市中海兴汽车配件厂</t>
+          <t>平原滤清器有限公司</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>供应商济南海兴物料WG9931470260##库存不足一台份;</t>
+          <t>供应商平原滤清器仓库无库存&lt;br /&gt;供应商河北亿利仓库无库存&lt;br /&gt;供应商曼胡仓库无库存;</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>2344</v>
+        <v>2320</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ZZ01-DP15</t>
+          <t>ZZ01-ZF07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7716,43 +7716,43 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AZ992555500029</t>
+          <t>YG9725190064</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>轻量化油箱支架(675×500截面油箱)</t>
+          <t>油滤器中支架</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>AZ992555500029/1</t>
+          <t>YG9725190064/2</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>103264</t>
+          <t>101455</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>青岛宇远新材料有限公司</t>
+          <t>黄骅渤海机械制造有限公司</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>供应商青岛宇远仓库无库存&lt;br /&gt;供应商济南福瑞德物料AZ992555500029##库存不足一台份;</t>
+          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>2351</v>
+        <v>2338</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ZZ01-DP19</t>
+          <t>ZZ01-ZZ00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7789,52 +7789,52 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>100000794012</v>
+        <v>100000794037</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ZZ4257V424KF1L/W9EDV38-标运创富</t>
+          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45240.43506944444</v>
+        <v>45240.60659722222</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>YZ952536000197</t>
+          <t>WG9925860020</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中/后桥管束支架（汉德425ZGY）</t>
+          <t>备胎支架焊接总成</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>YZ952536000197/2</t>
+          <t>WG9925860020/1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>101595</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>山东鲲乾汽车配件有限公司</t>
+          <t>济南东冠汽车零部件有限公司</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>供应商鲲乾汽配物料YZ952536000197##库存不足一台份;</t>
+          <t>供应商济南东冠仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>2379</v>
+        <v>2347</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ZZ01-ND05</t>
+          <t>ZZ01-ZZ03</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100000794037</v>
+        <v>100000793984</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7882,47 +7882,47 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45240.54722222222</v>
+        <v>45240.72916666666</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>712W97420-0002</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>卡箍</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>712W97420-0002/1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>101822</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>济南晋升汽车配件厂</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商济南晋升物料712W97420-0002##库存不足一台份&lt;br /&gt;供应商济南富龙仓库无库存;</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -7936,7 +7936,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>2439</v>
+        <v>2398</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7945,69 +7945,69 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ZZ01-NS23</t>
+          <t>ZZ02-DF02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100000794037</v>
+        <v>100000793941</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.359375</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>712W28230-0007</t>
+          <t>850W41720-5025</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>控制器+遥控器（TX标配/马步奇电机）</t>
+          <t>低地板驾驶室前悬摆臂支架总成</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>712W28230-0007/1</t>
+          <t>850W41720-5025/2</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>北京经纬恒润科技股份有限公司</t>
+          <t>济南豪曼汽车配件有限公司</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>供应商北京经纬恒润库存不足(成组物料/订单一致性);</t>
+          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -8021,7 +8021,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>2461</v>
+        <v>2435</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -8030,12 +8030,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ZZ01-ZD01</t>
+          <t>ZZ02-DP07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8044,52 +8044,52 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100000794037</v>
+        <v>100000793963</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ4257V324HF1W/BCGBM32-标运质赢</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.71979166667</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>WG9000360714</t>
+          <t>YG9725684105</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>储气筒总成Φ275/40L</t>
+          <t>减震器上支架总成</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>WG9000360714/6</t>
+          <t>YG9725684105/2</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>137050</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>重庆市亚华汽车配件有限责任公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>供应商重庆市亚华汽车配件有物料WG9000360714##库存不足一台份&lt;br /&gt;供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南亨利元仓库无库存;</t>
+          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商济南汇英物料YG9725684105##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>2521</v>
+        <v>2450</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -8115,66 +8115,66 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ZZ01-ZF01</t>
+          <t>ZZ02-DP09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100000794024</v>
+        <v>100000793947</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ZZ4257V344KF1/WCEDV32-标运创富</t>
+          <t>ZZ4257V344HC1/U2GBM34-ZZ</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45240.38125</v>
+        <v>45240.73229166667</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>YZ952555000148</t>
+          <t>WG9925682111</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>油箱拉带(700×700截面油箱)</t>
+          <t>固定夹块</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>YZ952555000148/3</t>
+          <t>WG9925682111/3</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>103289</t>
+          <t>102377</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>清河县捷迈汽车零部件有限公司</t>
+          <t>济南云海汽车配件有限公司</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>供应商清河捷迈物料YZ952555000148##库存不足一台份;</t>
+          <t>供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份&lt;br /&gt;供应商交城太行汽车零部件制仓库无库存;</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>2538</v>
+        <v>2495</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -8200,12 +8200,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ZZ01-ZF04</t>
+          <t>ZZ02-DQ01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8214,52 +8214,52 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>100000794037</v>
+        <v>100000793932</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.57534722222</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>YZ160082120020</t>
+          <t>WG9925682111</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>固定夹块</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>YZ160082120020/2</t>
+          <t>WG9925682111/3</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>102096</t>
+          <t>102377</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>济南市中海兴汽车配件厂</t>
+          <t>济南云海汽车配件有限公司</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>供应商济南海兴仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存;</t>
+          <t>供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份&lt;br /&gt;供应商交城太行汽车零部件制仓库无库存;</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>2544</v>
+        <v>2496</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -8285,62 +8285,62 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ZZ01-ZF06</t>
+          <t>ZZ02-DQ01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>100000794009</v>
+        <v>100000794077</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45240.76354166667</v>
+        <v>45240.46319444444</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>811W41722-6032</t>
+          <t>WG9925682111</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
+          <t>固定夹块</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>811W41722-6032/1</t>
+          <t>WG9925682111/4</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>104290</t>
+          <t>113889</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>隆昌山川机械有限责任公司</t>
+          <t>交城太行汽车零部件制造有限公司</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>供应商山川减振器仓库无库存&lt;br /&gt;供应商江苏环球洪浩仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份;</t>
+          <t>供应商交城太行汽车零部件制仓库无库存&lt;br /&gt;供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -8361,7 +8361,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>2545</v>
+        <v>2514</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -8370,69 +8370,69 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ZZ01-ZF06</t>
+          <t>ZZ02-ND01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>100000794030</v>
+        <v>100000791936</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>AH1662..10503</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45240.68854166667</v>
+        <v>45240.34375</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>811W41722-6032</t>
+          <t>YZ16D269000031</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
+          <t>发动机罩隔热垫（高阻燃性）</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>811W41722-6032/2</t>
+          <t>YZ16D269000031/2</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>105274</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>镇江立达纤维工业有限责任公司</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩仓库无库存&lt;br /&gt;供应商山川减振器仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份;</t>
+          <t>供应商镇江立达仓库无库存&lt;br /&gt;供应商洛阳亚邦仓库无库存&lt;br /&gt;供应商江苏源力仓库无库存;</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>2546</v>
+        <v>2524</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -8455,69 +8455,69 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ZZ01-ZF07</t>
+          <t>ZZ02-ND05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100000794037</v>
+        <v>100000793941</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.371875</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>WG9X25190066</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>空滤器总成</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>WG9X25190066/1</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>102912</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>曼胡默尔滤清器（济南）有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>供应商曼胡仓库无库存&lt;br /&gt;供应商河北亿利仓库无库存&lt;br /&gt;供应商平原滤清器仓库无库存;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -8531,7 +8531,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>2547</v>
+        <v>2536</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -8540,69 +8540,69 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ZZ01-ZF07</t>
+          <t>ZZ02-NF04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100000794008</v>
+        <v>100000793904</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ4257V324GF1/BCFAV33-T标运</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45240.63854166667</v>
+        <v>45240.359375</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>WG9X25190066</t>
+          <t>850W41720-5025</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>空滤器总成</t>
+          <t>低地板驾驶室前悬摆臂支架总成</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>WG9X25190066/3</t>
+          <t>850W41720-5025/2</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>平原滤清器有限公司</t>
+          <t>济南豪曼汽车配件有限公司</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>供应商平原滤清器仓库无库存&lt;br /&gt;供应商河北亿利仓库无库存&lt;br /&gt;供应商曼胡仓库无库存;</t>
+          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存;</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -8616,7 +8616,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>2548</v>
+        <v>2669</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -8625,69 +8625,69 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ZZ01-ZF07</t>
+          <t>ZZ02-NS12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>100000794037</v>
+        <v>100000791937</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>YH166F--1000001</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.346875</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>YG9725190064</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>油滤器中支架</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>YG9725190064/2</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>101455</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>黄骅渤海机械制造有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>2569</v>
+        <v>2721</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -8710,69 +8710,69 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ZZ01-ZZ00</t>
+          <t>ZZ02-NS16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>100000794037</v>
+        <v>100000795180</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>AH1662..10702</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.35625</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>WG9925860020</t>
+          <t>811W41722-6022</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>备胎支架焊接总成</t>
+          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>WG9925860020/1</t>
+          <t>811W41722-6022/2</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>101595</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>济南东冠汽车零部件有限公司</t>
+          <t>江苏环球洪浩车业有限公司</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>供应商济南东冠仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
+          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>2578</v>
+        <v>2839</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -8795,12 +8795,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ZZ01-ZZ03</t>
+          <t>ZZ02-NW03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8809,52 +8809,52 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>100000793984</v>
+        <v>100000794173</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45240.72916666666</v>
+        <v>45240.54409722222</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>712W97420-0002</t>
+          <t>711W61900-7134</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>卡箍</t>
+          <t>空调机总成</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>712W97420-0002/1</t>
+          <t>711W61900-7134/8</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>101822</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>济南晋升汽车配件厂</t>
+          <t>湖北美标汽车制冷系统有限公司</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>供应商济南晋升物料712W97420-0002##库存不足一台份&lt;br /&gt;供应商济南富龙仓库无库存;</t>
+          <t>供应商湖北美标汽车制冷系统库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -8871,7 +8871,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>2580</v>
+        <v>2870</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ZZ01-ZZ03</t>
+          <t>ZZ02-ZD01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8894,48 +8894,48 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>100000794037</v>
+        <v>100000794173</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ZZ3317V386GB1/V0FCV38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45240.60659722222</v>
+        <v>45240.56284722222</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>WG9725543351</t>
+          <t>WG9000360782</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>上限位板</t>
+          <t>铝合金储气筒总成Φ276/40L</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>WG9725543351/1</t>
+          <t>WG9000360782/1</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>济南豪曼汽车配件有限公司</t>
+          <t>淄博鲁川汽车配件有限公司</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商济南杰安永泰仓库无库存&lt;br /&gt;供应商汇泉机械物料WG9725543351##库存不足一台份;</t>
+          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -8956,7 +8956,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>2626</v>
+        <v>2930</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8970,57 +8970,57 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ZZ02-DF01</t>
+          <t>ZZ02-ZF06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100000793932</v>
+        <v>100000793941</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45240.57534722222</v>
+        <v>45240.371875</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>WG9750680075</t>
+          <t>811W41722-6032</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>平衡夹总成</t>
+          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>WG9750680075/5</t>
+          <t>811W41722-6032/1</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>104290</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>济南杰安永泰机械设备有限公司</t>
+          <t>隆昌山川机械有限责任公司</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>供应商济南杰安永泰仓库无库存&lt;br /&gt;供应商济南金瑞阳物料WG9750680075##库存不足一台份&lt;br /&gt;供应商济南圣凯物料WG9750680075##库存不足一台份;</t>
+          <t>供应商山川减振器仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份&lt;br /&gt;供应商江苏环球洪浩仓库无库存;</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
         <v>0</v>
@@ -9041,7 +9041,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>2627</v>
+        <v>2936</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -9055,16 +9055,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ZZ02-DF01</t>
+          <t>ZZ02-ZF07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>100000794114</v>
+        <v>100000793941</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -9072,47 +9072,47 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45240.43506944444</v>
+        <v>45240.371875</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>WG9750680075</t>
+          <t>YG9725190064</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>平衡夹总成</t>
+          <t>油滤器中支架</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>WG9750680075/B</t>
+          <t>YG9725190064/2</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>101455</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>济南金瑞阳机械制造有限公司</t>
+          <t>黄骅渤海机械制造有限公司</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>仓库无库存!;</t>
+          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
         </is>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -9126,7 +9126,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>2635</v>
+        <v>2937</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ZZ02-DF02</t>
+          <t>ZZ02-ZF07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9157,47 +9157,47 @@
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45240.359375</v>
+        <v>45240.371875</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>850W41720-5025</t>
+          <t>YG9725190070</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>低地板驾驶室前悬摆臂支架总成</t>
+          <t>油滤器后支架</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>850W41720-5025/2</t>
+          <t>YG9725190070/2</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>101455</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>济南豪曼汽车配件有限公司</t>
+          <t>黄骅渤海机械制造有限公司</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存;</t>
+          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
         </is>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -9211,7 +9211,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>2672</v>
+        <v>2940</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -9225,57 +9225,57 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ZZ02-DP07</t>
+          <t>ZZ02-ZF08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100000793963</v>
+        <v>100000793941</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ZZ4257V324HF1W/BCGBM32-标运质赢</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45240.71979166667</v>
+        <v>45240.359375</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>YG9725684105</t>
+          <t>WG9000360782</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>减震器上支架总成</t>
+          <t>铝合金储气筒总成Φ276/40L</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>YG9725684105/2</t>
+          <t>WG9000360782/1</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>济南金瑞阳机械制造有限公司</t>
+          <t>淄博鲁川汽车配件有限公司</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商济南汇英物料YG9725684105##库存不足一台份;</t>
+          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -9296,7 +9296,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>2688</v>
+        <v>2942</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ZZ02-DP09</t>
+          <t>ZZ02-ZF09</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9319,55 +9319,55 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100000793947</v>
+        <v>100000794114</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ZZ4257V344HC1/U2GBM34-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45240.73229166667</v>
+        <v>45240.43506944444</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>WG9925682111</t>
+          <t>752W41615-5101</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>固定夹块</t>
+          <t>左保险杠支架总成</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>WG9925682111/3</t>
+          <t>752W41615-5101/2</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>103507</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>济南云海汽车配件有限公司</t>
+          <t>山东弗泽瑞金属科技有限公司</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商交城太行汽车零部件制仓库无库存&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份;</t>
+          <t>供应商山东弗泽瑞仓库无库存;</t>
         </is>
       </c>
       <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
         <v>1</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>2705</v>
+        <v>2944</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ZZ02-DP15</t>
+          <t>ZZ02-ZF09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9404,52 +9404,52 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100000793947</v>
+        <v>100000793934</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ZZ4257V344HC1/U2GBM34-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45240.71354166666</v>
+        <v>45240.53159722222</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>WG9325550560</t>
+          <t>752W41615-5107</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>油箱支架(700×700)</t>
+          <t>保险杠下段支架总成</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>WG9325550560/4</t>
+          <t>752W41615-5107/1</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>101298</t>
+          <t>102042</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>河北信久重型机械制造有限公司</t>
+          <t>济南盛鑫达机械有限责任公司</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>供应商河北信久物料WG9325550560##库存不足一台份&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商济南众联广谊仓库无库存&lt;br /&gt;供应商山东鑫润仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商济南盛鑫达仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存;</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -9466,7 +9466,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>2706</v>
+        <v>2945</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9480,57 +9480,57 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ZZ02-DP15</t>
+          <t>ZZ02-ZF09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100000793957</v>
+        <v>100000793941</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ZZ4257V344HC1/U2GBM34-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45240.74166666667</v>
+        <v>45240.371875</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>WG9325550560</t>
+          <t>752W41615-5107</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>油箱支架(700×700)</t>
+          <t>保险杠下段支架总成</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>WG9325550560/5</t>
+          <t>752W41615-5107/3</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>101248</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>河北驰通车辆部件科技有限公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>供应商河北驰通仓库无库存&lt;br /&gt;供应商河北信久物料WG9325550560##库存不足一台份&lt;br /&gt;供应商济南众联广谊仓库无库存&lt;br /&gt;供应商山东鑫润仓库无库存&lt;br /&gt;供应商济南豪曼汽车配件有限公司仓库无库存;</t>
+          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南盛鑫达仓库无库存;</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -9551,7 +9551,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>2735</v>
+        <v>2946</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ZZ02-DQ01</t>
+          <t>ZZ02-ZF09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9574,52 +9574,52 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100000793932</v>
+        <v>100000794155</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
+          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45240.57534722222</v>
+        <v>45240.47256944444</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>WG9925682111</t>
+          <t>811W25101-6017</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>固定夹块</t>
+          <t>TX前照灯总成(左/带橡胶圈)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>WG9925682111/3</t>
+          <t>811W25101-6017/3</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>102536</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>济南云海汽车配件有限公司</t>
+          <t>江苏秦龙汽车科技有限公司</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商交城太行汽车零部件制仓库无库存&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份;</t>
+          <t>指定供方江苏秦龙库存不足;</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -9636,7 +9636,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>2736</v>
+        <v>2947</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ZZ02-DQ01</t>
+          <t>ZZ02-ZF09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9659,7 +9659,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100000794077</v>
+        <v>100000794075</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -9667,40 +9667,40 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45240.46319444444</v>
+        <v>45240.44756944444</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>WG9925682111</t>
+          <t>811W25101-6018</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>固定夹块</t>
+          <t>TX前照灯总成(右/带橡胶圈)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>WG9925682111/4</t>
+          <t>811W25101-6018/3</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>113889</t>
+          <t>102536</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>交城太行汽车零部件制造有限公司</t>
+          <t>江苏秦龙汽车科技有限公司</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>供应商交城太行汽车零部件制仓库无库存&lt;br /&gt;供应商济南云海物料WG9925682111##库存不足一台份&lt;br /&gt;供应商济南润成信德物料WG9925682111##库存不足一台份;</t>
+          <t>指定供方江苏秦龙库存不足;</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -9721,7 +9721,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>2754</v>
+        <v>2957</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -9735,64 +9735,64 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ZZ02-ND01</t>
+          <t>ZZ02-ZF10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100000791936</v>
+        <v>100000794173</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>AH1662..10503</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45240.34375</v>
+        <v>45240.49131944445</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>YZ16D269000031</t>
+          <t>712W42940-4039</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>发动机罩隔热垫（高阻燃性）</t>
+          <t>右尾灯支架</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>YZ16D269000031/2</t>
+          <t>712W42940-4039/3</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>105274</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>镇江立达纤维工业有限责任公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>供应商镇江立达仓库无库存&lt;br /&gt;供应商江苏源力仓库无库存&lt;br /&gt;供应商洛阳亚邦仓库无库存;</t>
+          <t>供应商济南金瑞阳库存不足(成组物料);</t>
         </is>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -9806,7 +9806,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>2765</v>
+        <v>2977</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -9820,64 +9820,64 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ZZ02-ND05</t>
+          <t>ZZ02-ZZ00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100000793941</v>
+        <v>100000794173</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45240.371875</v>
+        <v>45240.56284722222</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>WG9925860020</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>备胎支架焊接总成</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>WG9925860020/1</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>101595</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>济南东冠汽车零部件有限公司</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商济南东冠仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>2777</v>
+        <v>3042</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -9905,64 +9905,64 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ZZ02-NF04</t>
+          <t>ZZ02-ZZ13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100000793904</v>
+        <v>100000793932</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ZZ4257V324GF1/BCFAV33-T标运</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45240.359375</v>
+        <v>45240.57534722222</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>850W41720-5025</t>
+          <t>WG9325590220</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>低地板驾驶室前悬摆臂支架总成</t>
+          <t>管夹</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>850W41720-5025/2</t>
+          <t>WG9325590220/1</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>101985</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>济南豪曼汽车配件有限公司</t>
+          <t>济南任通汽车配件厂</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>供应商济南豪曼汽车配件有限公司仓库无库存&lt;br /&gt;供应商文安县北方谊联汽车零部件有限公司仓库无库存&lt;br /&gt;供应商济南汇英仓库无库存;</t>
+          <t>供应商济南任通物料WG9325590220##库存不足一台份&lt;br /&gt;供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存&lt;br /&gt;供应商济南万顺特仓库无库存;</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>2911</v>
+        <v>3043</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -9990,64 +9990,64 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ZZ02-NS12</t>
+          <t>ZZ02-ZZ13</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100000791937</v>
+        <v>100000794123</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>YH166F--1000001</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45240.346875</v>
+        <v>45240.66666666666</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>WG9325590220</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>管夹</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>WG9325590220/3</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>102034</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>济南圣凯工贸有限公司</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商济南圣凯仓库无库存&lt;br /&gt;供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南任通物料WG9325590220##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存;</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -10061,7 +10061,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>2964</v>
+        <v>3046</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -10075,64 +10075,64 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ZZ02-NS16</t>
+          <t>ZZ02-ZZ13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>100000795180</v>
+        <v>100000794123</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>AH1662..10702</t>
+          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45240.35625</v>
+        <v>45240.66666666666</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>811W41722-6022</t>
+          <t>YG9325590224</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>L32系列驾驶室前悬螺旋弹簧减振器总成</t>
+          <t>弯管</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>811W41722-6022/2</t>
+          <t>YG9325590224/2</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>江苏环球洪浩车业有限公司</t>
+          <t>济南金瑞阳机械制造有限公司</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>供应商江苏环球洪浩物料811W41722-6022##库存不足一台份&lt;br /&gt;供应商东风采埃孚物料811W41722-6022##库存不足一台份;</t>
+          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商济南任通仓库无库存;</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -10141,1536 +10141,6 @@
         <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>3083</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ZZ02-NW03</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>100000794173</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>45240.54409722222</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>711W61900-7134</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>空调机总成</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>711W61900-7134/8</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>101392</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>湖北美标汽车制冷系统有限公司</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="n">
-        <v>50</v>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>供应商湖北美标汽车制冷系统库存不足(成组物料);</t>
-        </is>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>3114</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ZZ02-ZD01</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>100000794173</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>45240.56284722222</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>752W51715-0024</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>储气筒支架(φ276)</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>752W51715-0024/2</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>103452</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>山东宝泉实业有限公司</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="n">
-        <v>200</v>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>供应商济南中宝泉仓库无库存&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南杰安永泰物料752W51715-0024##库存不足一台份&lt;br /&gt;供应商莱州金昌仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>3116</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>ZZ02-ZD01</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>100000794173</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>45240.56284722222</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>WG9000360782</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>铝合金储气筒总成Φ276/40L</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>WG9000360782/1</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>104389</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>淄博鲁川汽车配件有限公司</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="n">
-        <v>100</v>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
-        </is>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>3177</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF06</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>45240.371875</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>811W41722-6032</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>L32/40系列驾驶室后悬螺旋弹簧减振器总成</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>811W41722-6032/1</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>104290</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>隆昌山川机械有限责任公司</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="n">
-        <v>200</v>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>供应商山川减振器仓库无库存&lt;br /&gt;供应商江苏环球洪浩仓库无库存&lt;br /&gt;供应商东风采埃孚物料811W41722-6032##库存不足一台份;</t>
-        </is>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>3183</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF07</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>45240.371875</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>YG9725190064</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>油滤器中支架</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>YG9725190064/2</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>101455</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>黄骅渤海机械制造有限公司</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="n">
-        <v>100</v>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>29</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>3184</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF07</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>45240.371875</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>YG9725190070</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>油滤器后支架</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>YG9725190070/2</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>101455</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>黄骅渤海机械制造有限公司</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="n">
-        <v>100</v>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>供应商渤海汽配仓库无库存&lt;br /&gt;供应商大可仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>32</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>3185</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF08</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>45240.371875</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>752W51715-0024</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>储气筒支架(φ276)</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>752W51715-0024/2</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>103452</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>山东宝泉实业有限公司</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="n">
-        <v>200</v>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>供应商济南中宝泉仓库无库存&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南杰安永泰物料752W51715-0024##库存不足一台份&lt;br /&gt;供应商莱州金昌仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>3188</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF08</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>45240.359375</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>WG9000360782</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>铝合金储气筒总成Φ276/40L</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>WG9000360782/1</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>104389</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>淄博鲁川汽车配件有限公司</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="n">
-        <v>100</v>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>供应商淄博鲁川仓库无库存&lt;br /&gt;供应商济南润友仓库无库存&lt;br /&gt;供应商济南亨利元物料WG9000360782##库存不足一台份&lt;br /&gt;供应商重庆市亚华汽车配件有物料WG9000360782##库存不足一台份;</t>
-        </is>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>3190</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF09</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>100000794114</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>45240.43506944444</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>752W41615-5101</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>左保险杠支架总成</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>752W41615-5101/2</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>103507</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>山东弗泽瑞金属科技有限公司</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="n">
-        <v>76</v>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>供应商山东弗泽瑞仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>3192</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF09</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>100000793934</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>45240.53159722222</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>752W41615-5107</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>保险杠下段支架总成</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>752W41615-5107/1</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>102042</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>济南盛鑫达机械有限责任公司</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="n">
-        <v>60</v>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>供应商济南盛鑫达仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商济南金瑞阳仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>3193</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF09</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>100000793941</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>45240.371875</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>752W41615-5107</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>保险杠下段支架总成</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>752W41615-5107/3</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>101804</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>济南金瑞阳机械制造有限公司</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="n">
-        <v>30</v>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商渤海汽配仓库无库存&lt;br /&gt;供应商济南东冠仓库无库存&lt;br /&gt;供应商济南盛鑫达仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>3194</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF09</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>100000794155</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>45240.47256944444</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>811W25101-6017</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>TX前照灯总成(左/带橡胶圈)</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>811W25101-6017/3</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>102536</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>江苏秦龙汽车科技有限公司</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="n">
-        <v>63</v>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>指定供方江苏秦龙库存不足;</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>3195</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF09</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>100000794075</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>ZZ3257V384GE1/V7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>45240.44756944444</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>811W25101-6018</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>TX前照灯总成(右/带橡胶圈)</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>811W25101-6018/3</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>102536</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>江苏秦龙汽车科技有限公司</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="n">
-        <v>72</v>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>指定供方江苏秦龙库存不足;</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>3205</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>ZZ02-ZF10</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>100000794173</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>45240.49131944445</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>712W42940-4039</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>右尾灯支架</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>712W42940-4039/3</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>101804</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>济南金瑞阳机械制造有限公司</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="n">
-        <v>85</v>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>供应商济南金瑞阳库存不足(成组物料);</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>3225</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>ZZ02-ZZ00</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>100000794173</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>45240.56284722222</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>WG9925860020</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>备胎支架焊接总成</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>WG9925860020/1</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>101595</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>济南东冠汽车零部件有限公司</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="n">
-        <v>100</v>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>供应商济南东冠仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存&lt;br /&gt;供应商河北驰通仓库无库存&lt;br /&gt;供应商南皮宏图仓库无库存&lt;br /&gt;供应商齐河鑫瑞熙物料WG9925860020##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商济南乾华仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>3290</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>ZZ02-ZZ13</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>100000793932</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>45240.57534722222</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>WG9325590220</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>管夹</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>WG9325590220/1</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>101985</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>济南任通汽车配件厂</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="n">
-        <v>18</v>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>供应商济南任通物料WG9325590220##库存不足一台份&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南圣凯仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>1</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>3291</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>ZZ02-ZZ13</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>100000794123</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>45240.66666666666</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>WG9325590220</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>管夹</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>WG9325590220/3</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>102034</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>济南圣凯工贸有限公司</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="n">
-        <v>38</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>供应商济南圣凯仓库无库存&lt;br /&gt;供应商济南万顺特仓库无库存&lt;br /&gt;供应商青岛德顺昕仓库无库存&lt;br /&gt;供应商济南任通物料WG9325590220##库存不足一台份;</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>3295</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>ZZ02-ZZ13</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>100000794123</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>ZZ3317V386GE1/U7FBM38-ZZ</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>45240.66666666666</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>YG9325590224</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>弯管</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>YG9325590224/2</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>101804</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>济南金瑞阳机械制造有限公司</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="n">
-        <v>12</v>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>供应商济南金瑞阳仓库无库存&lt;br /&gt;供应商济南任通仓库无库存;</t>
-        </is>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
         <v>0</v>
       </c>
     </row>
